--- a/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que no han tenido retrasos en pagos</t>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,93; 100,0</t>
+          <t>96,41; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98,1; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98,21; 100,0</t>
+          <t>98,22; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,01; 89,06</t>
+          <t>35,66; 89,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,17; 93,29</t>
+          <t>82,69; 92,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,64; 89,77</t>
+          <t>52,86; 89,93</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,52; 96,22</t>
+          <t>83,0; 96,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,13; 98,96</t>
+          <t>89,26; 98,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,97; 96,62</t>
+          <t>88,49; 96,38</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,19; 93,14</t>
+          <t>77,68; 92,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,23; 98,6</t>
+          <t>85,79; 98,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,55; 94,85</t>
+          <t>85,02; 94,46</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,67; 100,0</t>
+          <t>93,96; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,11; 98,98</t>
+          <t>78,54; 99,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,7; 99,03</t>
+          <t>86,38; 99,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,58; 96,2</t>
+          <t>82,4; 95,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,83; 98,13</t>
+          <t>88,76; 98,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,99; 96,04</t>
+          <t>88,44; 96,16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,57; 93,74</t>
+          <t>84,08; 93,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84,38; 94,3</t>
+          <t>83,85; 94,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,35; 93,02</t>
+          <t>86,1; 92,92</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,2; 67,94</t>
+          <t>54,77; 68,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,35; 62,49</t>
+          <t>48,45; 63,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,4; 63,96</t>
+          <t>52,81; 63,57</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>69,67; 85,76</t>
+          <t>69,35; 85,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,47</t>
+          <t>82,9; 87,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,11; 85,81</t>
+          <t>77,02; 85,75</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>72037</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78057</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>150094</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>69955; 72563</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147936; 150620</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>86563</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112734</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>199298</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>44951; 112455</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>104656; 117688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>133530; 227179</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50980</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62783</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>113765</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>46365; 53685</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>58694; 64985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>107615; 117213</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>58303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69673</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>127976</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>52248; 62188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>63173; 72718</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>119781; 133089</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>34152</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37591</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>71743</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>32429; 34513</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31585; 39835</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>64554; 74002</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>41357</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52839</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>94197</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>37492; 43666</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49372; 54526</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>89432; 97235</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>107220</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>136863</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>244083</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>100567; 111932</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>127223; 142702</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>233624; 252129</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>80460</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>84623</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>165083</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>71618; 89566</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>73881; 97042</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>149592; 180047</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>531074</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>635163</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1166237</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>452247; 560631</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>616796; 652291</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1075361; 1197165</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,41; 100,0</t>
+          <t>96,03; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98,22; 100,0</t>
+          <t>98,28; 100,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,66; 89,22</t>
+          <t>31,86; 89,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,69; 92,99</t>
+          <t>83,14; 93,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,86; 89,93</t>
+          <t>55,49; 89,82</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,0; 96,1</t>
+          <t>83,6; 96,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,26; 98,83</t>
+          <t>88,55; 98,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,49; 96,38</t>
+          <t>88,66; 96,52</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,68; 92,46</t>
+          <t>77,62; 92,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,79; 98,75</t>
+          <t>83,7; 98,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,02; 94,46</t>
+          <t>85,11; 95,01</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,96; 100,0</t>
+          <t>94,73; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,54; 99,05</t>
+          <t>77,57; 99,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,38; 99,03</t>
+          <t>88,58; 99,02</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,4; 95,97</t>
+          <t>81,98; 96,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,76; 98,03</t>
+          <t>90,05; 97,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,44; 96,16</t>
+          <t>88,54; 96,16</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,08; 93,58</t>
+          <t>84,01; 93,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,85; 94,05</t>
+          <t>84,93; 94,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,1; 92,92</t>
+          <t>86,05; 92,67</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,77; 68,49</t>
+          <t>54,06; 68,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,45; 63,64</t>
+          <t>48,28; 62,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,81; 63,57</t>
+          <t>53,14; 63,47</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>69,35; 85,97</t>
+          <t>65,74; 85,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,9; 87,67</t>
+          <t>82,89; 87,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,02; 85,75</t>
+          <t>77,74; 85,92</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69955; 72563</t>
+          <t>69681; 72563</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147936; 150620</t>
+          <t>148030; 150620</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44951; 112455</t>
+          <t>40164; 112901</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104656; 117688</t>
+          <t>105232; 118127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133530; 227179</t>
+          <t>140175; 226905</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46365; 53685</t>
+          <t>46700; 53836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58694; 64985</t>
+          <t>58223; 64997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107615; 117213</t>
+          <t>107828; 117381</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52248; 62188</t>
+          <t>52208; 62312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63173; 72718</t>
+          <t>61635; 72400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119781; 133089</t>
+          <t>119917; 133858</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32429; 34513</t>
+          <t>32693; 34513</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31585; 39835</t>
+          <t>31197; 39839</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64554; 74002</t>
+          <t>66193; 73999</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37492; 43666</t>
+          <t>37298; 43861</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49372; 54526</t>
+          <t>50090; 54358</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89432; 97235</t>
+          <t>89537; 97237</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>100567; 111932</t>
+          <t>100490; 111911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>127223; 142702</t>
+          <t>128851; 142895</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233624; 252129</t>
+          <t>233474; 251451</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>71618; 89566</t>
+          <t>70688; 89704</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73881; 97042</t>
+          <t>73614; 95556</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>149592; 180047</t>
+          <t>150525; 179780</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>452247; 560631</t>
+          <t>428690; 559367</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>616796; 652291</t>
+          <t>616709; 652008</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1075361; 1197165</t>
+          <t>1085398; 1199550</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,03; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,54; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98,28; 100,0</t>
+          <t>98,06; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>88,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,86; 89,57</t>
+          <t>84,24; 94,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,14; 93,33</t>
+          <t>75,73; 92,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,49; 89,82</t>
+          <t>83,17; 91,99</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,6; 96,37</t>
+          <t>89,12; 98,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,55; 98,85</t>
+          <t>83,39; 96,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,66; 96,52</t>
+          <t>88,91; 96,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,62; 92,65</t>
+          <t>84,98; 98,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,7; 98,32</t>
+          <t>77,69; 93,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,11; 95,01</t>
+          <t>85,11; 94,6</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,73; 100,0</t>
+          <t>87,79; 99,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,57; 99,06</t>
+          <t>90,6; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,58; 99,02</t>
+          <t>92,79; 99,16</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,98; 96,4</t>
+          <t>88,56; 97,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,05; 97,73</t>
+          <t>82,77; 96,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,54; 96,16</t>
+          <t>87,76; 95,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,01; 93,56</t>
+          <t>83,56; 93,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84,93; 94,18</t>
+          <t>82,84; 93,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,05; 92,67</t>
+          <t>85,52; 92,6</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,06; 68,6</t>
+          <t>49,27; 63,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,28; 62,67</t>
+          <t>55,64; 69,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,14; 63,47</t>
+          <t>54,66; 65,37</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65,74; 85,78</t>
+          <t>82,46; 87,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,89; 87,63</t>
+          <t>81,19; 86,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,74; 85,92</t>
+          <t>82,7; 86,26</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>63025</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78057</t>
+          <t>55359</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150094</t>
+          <t>118384</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69681; 72563</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53323; 55814</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148030; 150620</t>
+          <t>116531; 118839</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>103372</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>112734</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199298</t>
+          <t>190334</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40164; 112901</t>
+          <t>96750; 108042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>105232; 118127</t>
+          <t>75591; 92028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140175; 226905</t>
+          <t>178541; 197465</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50980</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113765</t>
+          <t>105119</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46700; 53836</t>
+          <t>51824; 57524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58223; 64997</t>
+          <t>45216; 52194</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107828; 117381</t>
+          <t>99912; 108587</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127976</t>
+          <t>122894</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52208; 62312</t>
+          <t>57005; 66122</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61635; 72400</t>
+          <t>53087; 63603</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119917; 133858</t>
+          <t>115247; 128094</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34152</t>
+          <t>37577</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71743</t>
+          <t>72707</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32693; 34513</t>
+          <t>34369; 38873</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31197; 39839</t>
+          <t>32259; 35608</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66193; 73999</t>
+          <t>69368; 74127</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94197</t>
+          <t>86882</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37298; 43861</t>
+          <t>42822; 47287</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50090; 54358</t>
+          <t>37355; 43554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89537; 97237</t>
+          <t>82043; 89592</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>152</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>107220</t>
+          <t>122819</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>136863</t>
+          <t>105594</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244083</t>
+          <t>228413</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>100490; 111911</t>
+          <t>114534; 128423</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>128851; 142895</t>
+          <t>98092; 110723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233474; 251451</t>
+          <t>218505; 236591</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>113</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>80460</t>
+          <t>88325</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>84623</t>
+          <t>87897</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>165083</t>
+          <t>176222</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>70688; 89704</t>
+          <t>76558; 98952</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73614; 95556</t>
+          <t>77655; 96847</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>150525; 179780</t>
+          <t>161234; 192818</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>784</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>579849</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>635163</t>
+          <t>521106</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1166237</t>
+          <t>1100955</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>428690; 559367</t>
+          <t>563302; 595555</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>616709; 652008</t>
+          <t>500868; 534917</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1085398; 1199550</t>
+          <t>1075138; 1121333</t>
         </is>
       </c>
     </row>
